--- a/Output/Monthly Scan_19 Jul 2026.xlsx
+++ b/Output/Monthly Scan_19 Jul 2026.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -509,7 +509,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>56.68</v>
+        <v>45.39</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -521,14 +521,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -541,7 +541,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>45.13</v>
+        <v>56.68</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -553,14 +553,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>ABSLAMC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -573,11 +573,11 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>41.18</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -585,14 +585,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABSLAMC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -605,11 +605,11 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>53.01</v>
+        <v>90.27</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -617,14 +617,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACUTAAS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -637,11 +637,11 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>55.65</v>
+        <v>34.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -649,14 +649,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5PAISA</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -669,7 +669,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>49.05</v>
+        <v>48.91</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -681,14 +681,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAKASH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +701,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>41.13</v>
+        <v>52.78</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -713,7 +713,1159 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAREYDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>68.47</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>RSI &gt; 60</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>51.21</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABBOTINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AAVAS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3PLAND</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>RSI &lt; 40</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABFRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABMINTLLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>21STCENMGM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>63MOONS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A63MOONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ADVANIHOTR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>43.46</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADVANIHOTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABAN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>34.39</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>RSI &lt; 40</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>40.13</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>43.38</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADFFOODS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>RSI &gt; 60</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADFFOODS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AARTIDRUGS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>RSI &gt; 60</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AARVI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ADOR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>62.83</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>RSI &gt; 60</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20MICRONS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ADROITINFO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>RSI &lt; 40</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADROITINFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ACCELYA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCELYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ACCURACY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>RSI &lt; 40</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCURACY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5PAISA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>69.37</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>RSI &gt; 60</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A2ZINFRA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AA2ZINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>RSI &gt; 60</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AARON</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARON</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>67.42</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>RSI &gt; 60</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>70.63</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>RSI &gt; 60</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3IINFOLTD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3IINFOLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ABREL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>46.28</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AARTISURF</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>RSI 40–60</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTISURF</t>
         </is>
       </c>
     </row>
@@ -728,7 +1880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,7 +1948,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -815,14 +1967,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -841,14 +1993,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>ABSLAMC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -867,14 +2019,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABSLAMC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -884,11 +2036,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -897,14 +2045,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACUTAAS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,14 +2071,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5PAISA</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -940,7 +2088,11 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -949,14 +2101,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAKASH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -975,7 +2127,959 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAREYDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABBOTINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AAVAS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3PLAND</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABFRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABMINTLLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>21STCENMGM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>63MOONS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A63MOONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ADVANIHOTR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADVANIHOTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABAN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADFFOODS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADFFOODS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AARTIDRUGS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AARVI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ADOR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20MICRONS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ADROITINFO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADROITINFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ACCELYA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCELYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ACCURACY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCURACY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5PAISA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A2ZINFRA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AA2ZINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AARON</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARON</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3IINFOLTD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3IINFOLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ABREL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AARTISURF</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pullback Check</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTISURF</t>
         </is>
       </c>
     </row>
@@ -990,7 +3094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,7 +3162,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1077,14 +3181,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1103,14 +3207,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>ABSLAMC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1129,14 +3233,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABSLAMC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1155,14 +3259,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACUTAAS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1174,7 +3278,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bullish Confluence</t>
+          <t>Bearish Confluence</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -1185,14 +3289,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5PAISA</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1211,14 +3315,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAKASH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1228,7 +3332,11 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -1237,7 +3345,1015 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAREYDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABBOTINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AAVAS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3PLAND</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABFRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABMINTLLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>21STCENMGM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>63MOONS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A63MOONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ADVANIHOTR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADVANIHOTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABAN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADFFOODS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADFFOODS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AARTIDRUGS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AARVI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ADOR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20MICRONS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ADROITINFO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADROITINFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ACCELYA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCELYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ACCURACY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCURACY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5PAISA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A2ZINFRA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AA2ZINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AARON</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARON</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3IINFOLTD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3IINFOLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ABREL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AARTISURF</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Confluence Detected</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTISURF</t>
         </is>
       </c>
     </row>
@@ -1910,7 +5026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1998,6 +5114,136 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AARTIDRUGS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ADROITINFO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADROITINFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AARTISURF</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTISURF</t>
         </is>
       </c>
     </row>
@@ -2012,7 +5258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2080,7 +5326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2099,14 +5345,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2125,14 +5371,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>ABSLAMC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2151,14 +5397,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABSLAMC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2177,14 +5423,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACUTAAS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2203,14 +5449,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5PAISA</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2229,14 +5475,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAKASH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2255,7 +5501,943 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAREYDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABBOTINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AAVAS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3PLAND</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABFRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABMINTLLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>21STCENMGM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>63MOONS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A63MOONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ADVANIHOTR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADVANIHOTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABAN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADFFOODS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADFFOODS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AARTIDRUGS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AARVI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ADOR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20MICRONS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ADROITINFO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADROITINFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ACCELYA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCELYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ACCURACY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCURACY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5PAISA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A2ZINFRA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AA2ZINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AARON</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARON</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3IINFOLTD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3IINFOLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ABREL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AARTISURF</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTISURF</t>
         </is>
       </c>
     </row>
@@ -2270,7 +6452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2338,7 +6520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2357,14 +6539,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2383,14 +6565,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>ABSLAMC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2409,14 +6591,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABSLAMC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2426,7 +6608,11 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Probable Bearish Reversal</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -2435,14 +6621,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACUTAAS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2461,14 +6647,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5PAISA</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2487,14 +6673,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAKASH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2513,7 +6699,943 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAREYDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABBOTINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AAVAS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3PLAND</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABFRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABMINTLLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>21STCENMGM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>63MOONS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A63MOONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ADVANIHOTR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADVANIHOTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABAN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADFFOODS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADFFOODS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AARTIDRUGS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AARVI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ADOR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20MICRONS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ADROITINFO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADROITINFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ACCELYA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCELYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ACCURACY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCURACY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5PAISA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A2ZINFRA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AA2ZINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AARON</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARON</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3IINFOLTD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3IINFOLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ABREL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AARTISURF</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Reversal Watch</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTISURF</t>
         </is>
       </c>
     </row>
@@ -2528,7 +7650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2596,7 +7718,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2606,7 +7728,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -2619,14 +7741,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2636,7 +7758,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2649,14 +7771,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>ABSLAMC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2666,7 +7788,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -2679,14 +7801,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABSLAMC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2696,7 +7818,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -2709,14 +7831,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACUTAAS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2726,7 +7848,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -2739,14 +7861,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5PAISA</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2769,14 +7891,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAKASH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2786,7 +7908,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -2799,7 +7921,1087 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAREYDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Strong Bullish</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bullish Reversal Watch</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABBOTINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AAVAS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bearish Recovery Attempt</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3PLAND</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Strong Bearish</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Strong Bearish</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABFRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bearish Reversal Watch</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABMINTLLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>21STCENMGM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Strong Bearish</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>63MOONS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Weak Bullish</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A63MOONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ADVANIHOTR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Strong Bearish</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADVANIHOTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABAN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Strong Bearish</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bearish Reversal Watch</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Weak Bullish</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADFFOODS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Strong Bullish</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADFFOODS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AARTIDRUGS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bearish Recovery Attempt</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Strong Bullish</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AARVI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Strong Bullish</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ADOR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Strong Bullish</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20MICRONS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bullish Reversal Watch</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ADROITINFO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Strong Bearish</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADROITINFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ACCELYA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Strong Bearish</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCELYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Strong Bearish</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Strong Bullish</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ACCURACY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bearish Reversal Watch</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCURACY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5PAISA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bearish Reversal Watch</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Strong Bullish</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bearish Reversal Watch</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Strong Bullish</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A2ZINFRA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Strong Bearish</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AA2ZINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Strong Bullish</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AARON</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Strong Bearish</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARON</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bearish Recovery Attempt</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Strong Bullish</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Strong Bullish</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3IINFOLTD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bearish Reversal Watch</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3IINFOLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ABREL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bearish Recovery Attempt</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AARTISURF</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Bearish Recovery Attempt</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTISURF</t>
         </is>
       </c>
     </row>
@@ -2814,7 +9016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2882,20 +9084,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No scanner alerts detected for this interval</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>AAKASH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAKASH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AAVAS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABMINTLLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2908,7 +9242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2976,7 +9310,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ADL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2995,14 +9329,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3PLAND</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3010,11 +9344,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -3025,14 +9355,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21STCENMGM</t>
+          <t>ABSLAMC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3040,11 +9370,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -3055,14 +9381,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABSLAMC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20MICRONS</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3070,11 +9396,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -3085,14 +9407,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACUTAAS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3100,11 +9422,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -3115,14 +9433,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5PAISA</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3141,14 +9459,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAKASH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3IINFOLTD</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3156,11 +9474,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Strong Downtrend</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -3171,7 +9485,1027 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAREYDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABBOTINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AAVAS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAAVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3PLAND</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3PLAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABFRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABMINTLLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>21STCENMGM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A21STCENMGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>63MOONS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A63MOONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ADVANIHOTR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADVANIHOTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABAN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Strong Downtrend</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ACL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Strong Downtrend</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADFFOODS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADFFOODS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AARTIDRUGS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIDRUGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AARVI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ADOR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20MICRONS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A20MICRONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ADROITINFO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADROITINFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ACCELYA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCELYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3MINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ACCURACY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACCURACY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5PAISA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A5PAISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A2ZINFRA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AA2ZINFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AARON</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARON</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3IINFOLTD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Strong Downtrend</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A3IINFOLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ABREL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AARTISURF</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Uptrend/Downtrend</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAARTISURF</t>
         </is>
       </c>
     </row>
